--- a/questionnaire_templates/002_low_text_communication_preference_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/002_low_text_communication_preference_form--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -719,8 +719,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'text_message'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Text Message'}</t>
+          <t>Text Message</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'twice'}</t>
+          <t>twice</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Twice'}</t>
+          <t>Twice</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'as_needed'}</t>
+          <t>as_needed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'As Needed'}</t>
+          <t>As Needed</t>
         </is>
       </c>
     </row>
